--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T1_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T1_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>85</t>
+    <t>81</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.294</t>
+    <t>0.309</t>
+  </si>
+  <si>
+    <t>(0.052)</t>
+  </si>
+  <si>
+    <t>0.506</t>
+  </si>
+  <si>
+    <t>(0.056)</t>
+  </si>
+  <si>
+    <t>0.272</t>
   </si>
   <si>
     <t>(0.050)</t>
   </si>
   <si>
-    <t>0.482</t>
-  </si>
-  <si>
-    <t>(0.055)</t>
-  </si>
-  <si>
-    <t>0.259</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>0.918</t>
-  </si>
-  <si>
-    <t>(0.284)</t>
-  </si>
-  <si>
-    <t>1.247</t>
-  </si>
-  <si>
-    <t>(0.216)</t>
-  </si>
-  <si>
-    <t>0.435</t>
-  </si>
-  <si>
-    <t>(0.106)</t>
+    <t>0.963</t>
+  </si>
+  <si>
+    <t>(0.297)</t>
+  </si>
+  <si>
+    <t>1.309</t>
+  </si>
+  <si>
+    <t>(0.225)</t>
+  </si>
+  <si>
+    <t>0.457</t>
+  </si>
+  <si>
+    <t>(0.111)</t>
   </si>
   <si>
     <t>29</t>
@@ -138,7 +138,7 @@
     <t>(0.264)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.223**</t>
-  </si>
-  <si>
-    <t>0.311***</t>
-  </si>
-  <si>
-    <t>0.500***</t>
-  </si>
-  <si>
-    <t>1.186</t>
-  </si>
-  <si>
-    <t>1.960***</t>
-  </si>
-  <si>
-    <t>1.220***</t>
+    <t>0.209**</t>
+  </si>
+  <si>
+    <t>0.287***</t>
+  </si>
+  <si>
+    <t>0.487***</t>
+  </si>
+  <si>
+    <t>1.140</t>
+  </si>
+  <si>
+    <t>1.898***</t>
+  </si>
+  <si>
+    <t>1.198***</t>
   </si>
 </sst>
 </file>
